--- a/jira_export_2026-08-31.xlsx
+++ b/jira_export_2026-08-31.xlsx
@@ -6669,7 +6669,7 @@
         <v>5</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>38010.692</v>
       </c>
       <c r="P159" s="19" t="n">
-        <v>144.94</v>
+        <v>144.8</v>
       </c>
     </row>
   </sheetData>
@@ -12681,7 +12681,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>21</v>
+        <v>21.25</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>0</v>
@@ -12690,7 +12690,7 @@
         <v>1.25</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>22.25</v>
+        <v>22.5</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>6.5</v>
@@ -12700,7 +12700,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
     </row>
@@ -12800,13 +12800,13 @@
         <v>362163</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>133007</v>
+        <v>133227</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>229156</v>
+        <v>228936</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>145676</v>
+        <v>145456</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>21179</v>
@@ -12850,13 +12850,13 @@
         <v>196385</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>71329</v>
+        <v>71550</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>125056</v>
+        <v>124835</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>58766</v>
+        <v>58546</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>9871</v>

--- a/jira_export_2026-08-31.xlsx
+++ b/jira_export_2026-08-31.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>38,011 €</t>
+          <t>38,208 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>23,907 €</t>
+          <t>24,104 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>570 h</t>
+          <t>573 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -898,21 +898,21 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -928,7 +928,7 @@
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B29" s="7" t="n"/>
@@ -2465,10 +2465,10 @@
         <v>0</v>
       </c>
       <c r="O24" s="16" t="n">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="25">
@@ -6685,10 +6685,10 @@
         <v>588</v>
       </c>
       <c r="O83" s="17" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="P83" s="13" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
     </row>
     <row r="84">
@@ -10251,7 +10251,7 @@
         <v>20</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>8.25</v>
+        <v>10.75</v>
       </c>
       <c r="L134" s="15" t="inlineStr"/>
       <c r="M134" s="15" t="inlineStr"/>
@@ -11785,10 +11785,10 @@
         <v>46991.995</v>
       </c>
       <c r="O159" s="19" t="n">
-        <v>38010.692</v>
+        <v>38207.692</v>
       </c>
       <c r="P159" s="19" t="n">
-        <v>144.8</v>
+        <v>144.18</v>
       </c>
     </row>
   </sheetData>
@@ -12654,13 +12654,13 @@
         <v>187.5</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>36</v>
+        <v>38.5</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>16.5</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>240</v>
+        <v>242.5</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>84.5</v>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -12797,10 +12797,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>362163</v>
+        <v>361966</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>133227</v>
+        <v>133030</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>228936</v>
@@ -12847,10 +12847,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>196385</v>
+        <v>196188</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>71550</v>
+        <v>71353</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>124835</v>
@@ -13791,10 +13791,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -13812,7 +13812,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>11 clôture(s) : 9 projet(s), 2 rework</t>
+          <t>14 clôture(s) : 11 projet(s), 3 rework</t>
         </is>
       </c>
     </row>
@@ -13942,17 +13942,17 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34537</t>
+          <t>PDMDEP-34521</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BRON] - Remplacement de leur matériel par des PA</t>
+          <t>[COMMUNE DE FRONTON] - Simple commande de Pax pour installer</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRON</t>
+          <t>COMMUNE DE FRONTON</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -13972,22 +13972,22 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30044</t>
+          <t>PDMDEP-34537</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
+          <t>[COMMUNE DE BRON] - Remplacement de leur matériel par des PA</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>COMMUNE DE BRON</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -13996,28 +13996,28 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33781</t>
+          <t>PDMDEP-35219</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Modélisation de petits éléments </t>
+          <t xml:space="preserve">[COMMUNE DE FRONTON] - Abonnement carte sim correspondant à </t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT DIZIER</t>
+          <t>COMMUNE DE FRONTON</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -14026,18 +14026,18 @@
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-30044</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] - Installation serveurs et montée de version TEST ET</t>
+          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
@@ -14056,23 +14056,23 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34848</t>
+          <t>PDMDEP-33781</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BRUAY LA BUISSIERE] - Modification en-tête des a</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Modélisation de petits éléments </t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRUAY LA BUISSIERE</t>
+          <t>COMMUNE DE SAINT DIZIER</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -14086,126 +14086,216 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
+          <t>PDMDEP-33822</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>[CD 29] - Installation serveurs et montée de version TEST ET</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34848</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE BRUAY LA BUISSIERE] - Modification en-tête des a</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BRUAY LA BUISSIERE</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
           <t>PDMDEP-34966</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>[Commune de Villeneuve D'Ascq] - Ajout de 5 licences supplém</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Commune de Villeneuve D'Ascq</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="F13" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="F15" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>PDMDEP-29208</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Commune de Calais - GEODP2 new</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>Commune de Calais</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>PDMDEP-14798</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>[CD Hauts-de-Seine]</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E14" s="28" t="inlineStr">
+      <c r="E17" s="28" t="inlineStr">
         <is>
           <t>Rework</t>
         </is>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F17" s="28" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="28" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>PDMDEP-4395</t>
         </is>
       </c>
-      <c r="B15" s="28" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>[COLMAR] LITTERALIS PRIME</t>
         </is>
       </c>
-      <c r="C15" s="28" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>COLMAR</t>
         </is>
       </c>
-      <c r="D15" s="28" t="inlineStr">
+      <c r="D18" s="28" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E15" s="28" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>Rework</t>
         </is>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F18" s="28" t="n">
         <v>36</v>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n"/>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="18" t="n"/>
-      <c r="E17" s="18" t="n"/>
-      <c r="F17" s="18" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n"/>
-      <c r="C18" s="29" t="n"/>
-      <c r="D18" s="29" t="n"/>
-      <c r="E18" s="29" t="n"/>
-      <c r="F18" s="29" t="n">
-        <v>2</v>
+      <c r="B21" s="29" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="29" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-08-31.xlsx
+++ b/jira_export_2026-08-31.xlsx
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L7" s="12" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
@@ -9703,7 +9703,7 @@
         <v>16</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>38207.692</v>
       </c>
       <c r="P159" s="19" t="n">
-        <v>144.18</v>
+        <v>143.91</v>
       </c>
     </row>
   </sheetData>
@@ -12651,16 +12651,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>187.5</v>
+        <v>187.75</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>38.5</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>16.5</v>
+        <v>16.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>242.5</v>
+        <v>243</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>84.5</v>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.6%</t>
         </is>
       </c>
     </row>

--- a/jira_export_2026-08-31.xlsx
+++ b/jira_export_2026-08-31.xlsx
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>573 h</t>
+          <t>587 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>83.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P159"/>
+  <dimension ref="A1:P163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1257,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L7" s="12" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
@@ -1970,32 +1970,32 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34694</t>
+          <t>PDMDEP-34718</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
+          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>Commune du Tampon</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
@@ -2005,35 +2005,35 @@
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="J18" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34701</t>
+          <t>PDMDEP-34722</t>
         </is>
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>00176675</t>
+          <t>00176875</t>
         </is>
       </c>
       <c r="N18" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="16" t="n">
-        <v>789.5</v>
+        <v>0</v>
       </c>
       <c r="P18" s="16" t="n">
         <v>0</v>
@@ -2042,12 +2042,12 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34676</t>
+          <t>PDMDEP-34694</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP Placier</t>
+          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Commune des Ponts de Ce</t>
+          <t>Commune du Tampon</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -2093,19 +2093,19 @@
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34683</t>
+          <t>PDMDEP-34701</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>00176614</t>
+          <t>00176675</t>
         </is>
       </c>
       <c r="N19" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>430</v>
+        <v>789.5</v>
       </c>
       <c r="P19" s="13" t="n">
         <v>0</v>
@@ -2114,12 +2114,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34659</t>
+          <t>PDMDEP-34676</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP TLPE</t>
+          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="L20" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34666</t>
+          <t>PDMDEP-34683</t>
         </is>
       </c>
       <c r="M20" s="15" t="inlineStr">
@@ -2177,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="16" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="P20" s="16" t="n">
         <v>0</v>
@@ -2186,32 +2186,32 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34650</t>
+          <t>PDMDEP-34659</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>[CD 01] -  Transfert de compétence Montée de version</t>
+          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP TLPE</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>Commune des Ponts de Ce</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
+          <t>Migration GEODP TLPE</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
@@ -2221,35 +2221,35 @@
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J21" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34654</t>
+          <t>PDMDEP-34666</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>00176582</t>
+          <t>00176614</t>
         </is>
       </c>
       <c r="N21" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="P21" s="13" t="n">
         <v>0</v>
@@ -2258,32 +2258,32 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34631</t>
+          <t>PDMDEP-34650</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
+          <t>[CD 01] -  Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>acquisition geodp caisse</t>
+          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I22" s="15" t="inlineStr">
@@ -2305,23 +2305,23 @@
         <v>1</v>
       </c>
       <c r="K22" s="15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34640</t>
+          <t>PDMDEP-34654</t>
         </is>
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
-          <t>00176477</t>
+          <t>00176582</t>
         </is>
       </c>
       <c r="N22" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="16" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="P22" s="16" t="n">
         <v>0</v>
@@ -2330,27 +2330,27 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34613</t>
+          <t>PDMDEP-34631</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE FORT-DE-FRANCE] - Achat 4x PAX A920 et mise en service application et paiement CB sur les nouveaux appareils</t>
+          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FORT-DE-FRANCE</t>
+          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Achat 4x PAX A920 et mise en service application et paiement CB sur les nouveaux appareils</t>
+          <t>acquisition geodp caisse</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J23" s="12" t="n">
@@ -2381,19 +2381,19 @@
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34621</t>
+          <t>PDMDEP-34640</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>00176431</t>
+          <t>00176477</t>
         </is>
       </c>
       <c r="N23" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="P23" s="13" t="n">
         <v>0</v>
@@ -2402,12 +2402,12 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34521</t>
+          <t>PDMDEP-34613</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE FRONTON] - Simple commande de Pax pour installer Placier dessus</t>
+          <t>[COMMUNE DE FORT-DE-FRANCE] - Achat 4x PAX A920 et mise en service application et paiement CB sur les nouveaux appareils</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FRONTON</t>
+          <t>COMMUNE DE FORT-DE-FRANCE</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>Simple commande de Pax pour installer Placier dessus</t>
+          <t>Achat 4x PAX A920 et mise en service application et paiement CB sur les nouveaux appareils</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
@@ -2442,64 +2442,64 @@
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K24" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34527</t>
+          <t>PDMDEP-34621</t>
         </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>00173007</t>
+          <t>00176431</t>
         </is>
       </c>
       <c r="N24" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="16" t="n">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34521</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[COMMUNE DE FRONTON] - Simple commande de Pax pour installer Placier dessus</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>COMMUNE DE FRONTON</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t>Simple commande de Pax pour installer Placier dessus</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
@@ -2514,64 +2514,64 @@
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="J25" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34527</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00173007</t>
         </is>
       </c>
       <c r="N25" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O25" s="13" t="n">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="P25" s="13" t="n">
-        <v>64.5</v>
+        <v>900</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr">
@@ -2581,49 +2581,49 @@
       </c>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="15" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N26" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="16" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>0</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34337</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
+          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Commune de Chalons-sur-Saone</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Achat nouveau PAX A920</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -2653,35 +2653,35 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="J27" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34345</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>00171711</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="N27" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P27" s="13" t="n">
         <v>0</v>
@@ -2690,12 +2690,12 @@
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34337</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>Commune de Chalons-sur-Saone</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I28" s="15" t="inlineStr">
@@ -2741,19 +2741,19 @@
       </c>
       <c r="L28" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34345</t>
         </is>
       </c>
       <c r="M28" s="15" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00171711</t>
         </is>
       </c>
       <c r="N28" s="16" t="n">
-        <v>769.5</v>
-      </c>
-      <c r="O28" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O28" s="16" t="n">
+        <v>50</v>
       </c>
       <c r="P28" s="16" t="n">
         <v>0</v>
@@ -2762,27 +2762,27 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34303</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAP</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Migration Placier + ODP</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -2813,19 +2813,19 @@
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34310</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>00171605</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="13" t="n">
-        <v>1660</v>
+        <v>769.5</v>
+      </c>
+      <c r="O29" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P29" s="13" t="n">
         <v>0</v>
@@ -2834,12 +2834,12 @@
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34303</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE GAP</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>Migration Placier + ODP</t>
         </is>
       </c>
       <c r="F30" s="15" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J30" s="15" t="n">
@@ -2885,19 +2885,19 @@
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34310</t>
         </is>
       </c>
       <c r="M30" s="15" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171605</t>
         </is>
       </c>
       <c r="N30" s="16" t="n">
-        <v>2127.2</v>
-      </c>
-      <c r="O30" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O30" s="16" t="n">
+        <v>1660</v>
       </c>
       <c r="P30" s="16" t="n">
         <v>0</v>
@@ -2906,32 +2906,32 @@
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -2941,69 +2941,69 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J31" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>15.25</v>
+        <v>0</v>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N31" s="13" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O31" s="17" t="n">
-        <v>1296</v>
+        <v>0</v>
       </c>
       <c r="P31" s="13" t="n">
-        <v>84.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr">
@@ -3013,49 +3013,49 @@
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K32" s="15" t="n">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N32" s="16" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O32" s="17" t="n">
-        <v>367.5</v>
+        <v>1296</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>0</v>
+        <v>84.98</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -3065,12 +3065,12 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr">
@@ -3101,19 +3101,19 @@
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N33" s="13" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O33" s="17" t="n">
-        <v>0</v>
+        <v>367.5</v>
       </c>
       <c r="P33" s="13" t="n">
         <v>0</v>
@@ -3122,42 +3122,42 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34183</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MEGEVE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G34" s="15" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I34" s="15" t="inlineStr">
@@ -3169,14 +3169,22 @@
         <v>2</v>
       </c>
       <c r="K34" s="15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L34" s="15" t="inlineStr"/>
-      <c r="M34" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34201</t>
+        </is>
+      </c>
+      <c r="M34" s="15" t="inlineStr">
+        <is>
+          <t>00171162</t>
+        </is>
+      </c>
       <c r="N34" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="16" t="n">
+        <v>1662</v>
+      </c>
+      <c r="O34" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P34" s="16" t="n">
@@ -3186,70 +3194,62 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34183</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE MEGEVE] - Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE MEGEVE</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Mise à jour référentiel cartographie Littéralis Expert</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J35" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34227</t>
-        </is>
-      </c>
-      <c r="M35" s="12" t="inlineStr">
-        <is>
-          <t>2026-0210095</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L35" s="12" t="inlineStr"/>
+      <c r="M35" s="12" t="inlineStr"/>
       <c r="N35" s="13" t="n">
-        <v>9623.1</v>
-      </c>
-      <c r="O35" s="17" t="n">
-        <v>1603.85</v>
+        <v>0</v>
+      </c>
+      <c r="O35" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P35" s="13" t="n">
         <v>0</v>
@@ -3258,32 +3258,32 @@
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34126</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>[SETE] - AME LiEx</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>AME LiEx</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G36" s="15" t="inlineStr">
@@ -3293,35 +3293,35 @@
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K36" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L36" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34130</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
-          <t>00170928</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="16" t="n">
-        <v>0</v>
+        <v>9623.1</v>
+      </c>
+      <c r="O36" s="17" t="n">
+        <v>1603.85</v>
       </c>
       <c r="P36" s="16" t="n">
         <v>0</v>
@@ -3330,32 +3330,32 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34126</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[SETE] - AME LiEx</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>AME LiEx</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
@@ -3377,22 +3377,22 @@
         <v>2</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34130</t>
         </is>
       </c>
       <c r="M37" s="12" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>00170928</t>
         </is>
       </c>
       <c r="N37" s="13" t="n">
-        <v>707</v>
-      </c>
-      <c r="O37" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P37" s="13" t="n">
@@ -3402,12 +3402,12 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
@@ -3437,64 +3437,64 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J38" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K38" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N38" s="16" t="n">
-        <v>300</v>
+        <v>707</v>
       </c>
       <c r="O38" s="17" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34000</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Imprimante Bixolon</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Imprimante Bixolon</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
@@ -3514,36 +3514,44 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J39" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L39" s="12" t="inlineStr"/>
-      <c r="M39" s="12" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L39" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34070</t>
+        </is>
+      </c>
+      <c r="M39" s="12" t="inlineStr">
+        <is>
+          <t>00170468</t>
+        </is>
+      </c>
       <c r="N39" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="13" t="n">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="O39" s="17" t="n">
+        <v>90</v>
       </c>
       <c r="P39" s="13" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34000</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DE LA GARDE] - Imprimante Bixolon</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
@@ -3553,12 +3561,12 @@
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Imprimante Bixolon</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
@@ -3568,12 +3576,12 @@
       </c>
       <c r="G40" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I40" s="15" t="inlineStr">
@@ -3585,57 +3593,49 @@
         <v>2</v>
       </c>
       <c r="K40" s="15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L40" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33991</t>
-        </is>
-      </c>
-      <c r="M40" s="15" t="inlineStr">
-        <is>
-          <t>00170408</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L40" s="15" t="inlineStr"/>
+      <c r="M40" s="15" t="inlineStr"/>
       <c r="N40" s="16" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="O40" s="16" t="n">
-        <v>816</v>
+        <v>0</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>251.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
@@ -3645,64 +3645,64 @@
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J41" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>9.75</v>
+        <v>3.25</v>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M41" s="12" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N41" s="13" t="n">
-        <v>242.9</v>
+        <v>510</v>
       </c>
       <c r="O41" s="13" t="n">
-        <v>1118.61</v>
+        <v>816</v>
       </c>
       <c r="P41" s="13" t="n">
-        <v>114.73</v>
+        <v>251.08</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
@@ -3729,57 +3729,57 @@
         <v>2</v>
       </c>
       <c r="K42" s="15" t="n">
-        <v>0.5</v>
+        <v>9.75</v>
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N42" s="16" t="n">
-        <v>220</v>
-      </c>
-      <c r="O42" s="17" t="n">
-        <v>0</v>
+        <v>242.9</v>
+      </c>
+      <c r="O42" s="16" t="n">
+        <v>1118.61</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0</v>
+        <v>114.73</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
@@ -3789,34 +3789,34 @@
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J43" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M43" s="12" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="13" t="n">
+        <v>220</v>
+      </c>
+      <c r="O43" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="13" t="n">
@@ -3826,32 +3826,32 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>Installation serveurs et montée de version TEST ET PROD</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G44" s="15" t="inlineStr">
@@ -3861,49 +3861,49 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K44" s="15" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N44" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="16" t="n">
-        <v>787.5</v>
+        <v>0</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>393.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -3945,37 +3945,37 @@
         <v>2</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="M45" s="12" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="N45" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O45" s="13" t="n">
-        <v>449.155</v>
+        <v>787.5</v>
       </c>
       <c r="P45" s="13" t="n">
-        <v>44.92</v>
+        <v>393.75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
@@ -4017,52 +4017,52 @@
         <v>2</v>
       </c>
       <c r="K46" s="15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N46" s="16" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O46" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O46" s="16" t="n">
+        <v>449.155</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0</v>
+        <v>39.06</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -4082,44 +4082,44 @@
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J47" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M47" s="12" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="13" t="n">
-        <v>66.55</v>
+        <v>1890</v>
+      </c>
+      <c r="O47" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P47" s="13" t="n">
-        <v>133.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
@@ -4129,12 +4129,12 @@
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
@@ -4154,59 +4154,59 @@
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N48" s="16" t="n">
-        <v>920</v>
+        <v>0</v>
       </c>
       <c r="O48" s="16" t="n">
-        <v>966</v>
+        <v>66.55</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>483</v>
+        <v>133.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33699</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -4226,64 +4226,64 @@
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J49" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33703</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M49" s="12" t="inlineStr">
         <is>
-          <t>00169363</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N49" s="13" t="n">
-        <v>0</v>
+        <v>920</v>
       </c>
       <c r="O49" s="13" t="n">
-        <v>0</v>
+        <v>966</v>
       </c>
       <c r="P49" s="13" t="n">
-        <v>0</v>
+        <v>483</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33638</t>
+          <t>PDMDEP-33699</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
+          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOULINS</t>
+          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier et MEP module Caisse</t>
+          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G50" s="15" t="inlineStr">
@@ -4293,49 +4293,49 @@
       </c>
       <c r="H50" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K50" s="15" t="n">
-        <v>4</v>
+        <v>0.25</v>
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33647</t>
+          <t>PDMDEP-33703</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>00169251</t>
+          <t>00169363</t>
         </is>
       </c>
       <c r="N50" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O50" s="16" t="n">
-        <v>3855.2</v>
+        <v>0</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>963.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33638</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
+          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>COMMUNE DE MOULINS</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Migration GeODP Placier et MEP module Caisse</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -4370,59 +4370,59 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="J51" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33647</t>
         </is>
       </c>
       <c r="M51" s="12" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169251</t>
         </is>
       </c>
       <c r="N51" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O51" s="13" t="n">
-        <v>3535</v>
+        <v>3855.2</v>
       </c>
       <c r="P51" s="13" t="n">
-        <v>1571.11</v>
+        <v>963.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I52" s="15" t="inlineStr">
@@ -4449,57 +4449,57 @@
         <v>2</v>
       </c>
       <c r="K52" s="15" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N52" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O52" s="16" t="n">
-        <v>691.9</v>
+        <v>3535</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>691.9</v>
+        <v>1571.11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
@@ -4514,64 +4514,64 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J53" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M53" s="12" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N53" s="13" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O53" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O53" s="13" t="n">
+        <v>691.9</v>
       </c>
       <c r="P53" s="13" t="n">
-        <v>0</v>
+        <v>691.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G54" s="15" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
@@ -4597,19 +4597,19 @@
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N54" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="16" t="n">
-        <v>1460.9</v>
+        <v>171.4</v>
+      </c>
+      <c r="O54" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P54" s="16" t="n">
         <v>0</v>
@@ -4618,27 +4618,27 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J55" s="12" t="n">
@@ -4669,19 +4669,19 @@
       </c>
       <c r="L55" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M55" s="12" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N55" s="13" t="n">
-        <v>344</v>
-      </c>
-      <c r="O55" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O55" s="13" t="n">
+        <v>1460.9</v>
       </c>
       <c r="P55" s="13" t="n">
         <v>0</v>
@@ -4690,32 +4690,32 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G56" s="15" t="inlineStr">
@@ -4737,37 +4737,37 @@
         <v>3</v>
       </c>
       <c r="K56" s="15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L56" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M56" s="15" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N56" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="16" t="n">
-        <v>642.75</v>
+        <v>344</v>
+      </c>
+      <c r="O56" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>514.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33311</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>AMIENS METROPOLE</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -4802,64 +4802,64 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J57" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L57" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33315</t>
+          <t>PDMDEP-33390</t>
         </is>
       </c>
       <c r="M57" s="12" t="inlineStr">
         <is>
-          <t>00167138</t>
+          <t>00167823</t>
         </is>
       </c>
       <c r="N57" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O57" s="13" t="n">
-        <v>224.76</v>
+        <v>642.75</v>
       </c>
       <c r="P57" s="13" t="n">
-        <v>0</v>
+        <v>514.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33311</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G58" s="15" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J58" s="15" t="n">
@@ -4885,19 +4885,19 @@
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33315</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167138</t>
         </is>
       </c>
       <c r="N58" s="16" t="n">
-        <v>500</v>
-      </c>
-      <c r="O58" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O58" s="16" t="n">
+        <v>224.76</v>
       </c>
       <c r="P58" s="16" t="n">
         <v>0</v>
@@ -4906,27 +4906,27 @@
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J59" s="12" t="n">
@@ -4957,16 +4957,16 @@
       </c>
       <c r="L59" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M59" s="12" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N59" s="13" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O59" s="17" t="n">
         <v>0</v>
@@ -4978,32 +4978,32 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G60" s="15" t="inlineStr">
@@ -5013,38 +5013,38 @@
       </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K60" s="15" t="n">
-        <v>8.619999999999999</v>
+        <v>0</v>
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>625</v>
-      </c>
-      <c r="O60" s="16" t="n">
-        <v>652.5</v>
+        <v>149</v>
+      </c>
+      <c r="O60" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>75.65000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5101,53 +5101,53 @@
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M61" s="12" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N61" s="13" t="n">
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="O61" s="13" t="n">
-        <v>192</v>
+        <v>652.5</v>
       </c>
       <c r="P61" s="13" t="n">
-        <v>22.26</v>
+        <v>75.65000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G62" s="15" t="inlineStr">
@@ -5157,49 +5157,49 @@
       </c>
       <c r="H62" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J62" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K62" s="15" t="n">
-        <v>5</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N62" s="16" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="O62" s="16" t="n">
-        <v>910</v>
+        <v>192</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>182</v>
+        <v>22.26</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -5234,59 +5234,59 @@
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J63" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L63" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M63" s="12" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N63" s="13" t="n">
-        <v>1207</v>
-      </c>
-      <c r="O63" s="17" t="n">
-        <v>0</v>
+        <v>910</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>910</v>
       </c>
       <c r="P63" s="13" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
@@ -5306,64 +5306,64 @@
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K64" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="16" t="n">
-        <v>431.6</v>
+        <v>1207</v>
+      </c>
+      <c r="O64" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>1726.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
@@ -5373,69 +5373,69 @@
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J65" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L65" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M65" s="12" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N65" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="O65" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O65" s="13" t="n">
+        <v>431.6</v>
       </c>
       <c r="P65" s="13" t="n">
-        <v>0</v>
+        <v>1726.4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G66" s="15" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I66" s="15" t="inlineStr">
@@ -5457,22 +5457,22 @@
         <v>4</v>
       </c>
       <c r="K66" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="16" t="n">
+        <v>500</v>
+      </c>
+      <c r="O66" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="16" t="n">
@@ -5482,12 +5482,12 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32950</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 1/2 (Pax + Mise en service)</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 1/2</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -5529,23 +5529,23 @@
         <v>4</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32958</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M67" s="12" t="inlineStr">
         <is>
-          <t>00165249</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N67" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O67" s="13" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="P67" s="13" t="n">
         <v>0</v>
@@ -5554,32 +5554,32 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32950</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 1/2 (Pax + Mise en service)</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Migration GeODP Placier 1/2</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G68" s="15" t="inlineStr">
@@ -5589,35 +5589,35 @@
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32958</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165249</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O68" s="16" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="P68" s="16" t="n">
         <v>0</v>
@@ -5626,12 +5626,12 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
@@ -5641,12 +5641,12 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -5666,44 +5666,44 @@
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J69" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>2.75</v>
+        <v>0.25</v>
       </c>
       <c r="L69" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M69" s="12" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N69" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O69" s="13" t="n">
-        <v>219.36</v>
+        <v>0</v>
       </c>
       <c r="P69" s="13" t="n">
-        <v>79.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32565</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
@@ -5713,12 +5713,12 @@
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Afficher les AP signé avant MEP WFS</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="G70" s="15" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H70" s="15" t="inlineStr">
@@ -5738,36 +5738,44 @@
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K70" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="L70" s="15" t="inlineStr"/>
-      <c r="M70" s="15" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L70" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-32629</t>
+        </is>
+      </c>
+      <c r="M70" s="15" t="inlineStr">
+        <is>
+          <t>00163182</t>
+        </is>
+      </c>
       <c r="N70" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O70" s="16" t="n">
-        <v>0</v>
+        <v>219.36</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32565</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -5777,12 +5785,12 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -5792,7 +5800,7 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H71" s="12" t="inlineStr">
@@ -5809,22 +5817,14 @@
         <v>4</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-32556</t>
-        </is>
-      </c>
-      <c r="M71" s="12" t="inlineStr">
-        <is>
-          <t>00162313</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L71" s="12" t="inlineStr"/>
+      <c r="M71" s="12" t="inlineStr"/>
       <c r="N71" s="13" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O71" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="13" t="n">
@@ -5834,32 +5834,32 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G72" s="15" t="inlineStr">
@@ -5869,32 +5869,32 @@
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K72" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N72" s="16" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O72" s="17" t="n">
         <v>0</v>
@@ -5906,32 +5906,32 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
@@ -5941,34 +5941,34 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J73" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M73" s="12" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N73" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="13" t="n">
+        <v>2335</v>
+      </c>
+      <c r="O73" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="13" t="n">
@@ -5978,32 +5978,32 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
@@ -6013,34 +6013,34 @@
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K74" s="15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="O74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="16" t="n">
@@ -6050,32 +6050,32 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -6085,65 +6085,69 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J75" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L75" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M75" s="12" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N75" s="13" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O75" s="17" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="P75" s="13" t="n">
-        <v>60.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C76" s="15" t="inlineStr"/>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
@@ -6153,64 +6157,60 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K76" s="15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="16" t="n">
-        <v>127.5</v>
+        <v>910</v>
+      </c>
+      <c r="O76" s="17" t="n">
+        <v>91</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
-        </is>
-      </c>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr"/>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
@@ -6237,52 +6237,52 @@
         <v>5</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M77" s="12" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N77" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O77" s="13" t="n">
-        <v>100</v>
+        <v>127.5</v>
       </c>
       <c r="P77" s="13" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
@@ -6313,53 +6313,53 @@
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>590.15</v>
+        <v>0</v>
       </c>
       <c r="O78" s="16" t="n">
-        <v>793.65</v>
+        <v>100</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>3174.6</v>
+        <v>400</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
@@ -6374,64 +6374,64 @@
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J79" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>12.75</v>
+        <v>0.25</v>
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N79" s="13" t="n">
-        <v>0</v>
+        <v>590.15</v>
       </c>
       <c r="O79" s="13" t="n">
-        <v>109.972</v>
+        <v>793.65</v>
       </c>
       <c r="P79" s="13" t="n">
-        <v>8.630000000000001</v>
+        <v>3174.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
@@ -6441,69 +6441,69 @@
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>285</v>
-      </c>
-      <c r="O80" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O80" s="16" t="n">
+        <v>109.972</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>0</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J81" s="12" t="n">
@@ -6529,16 +6529,16 @@
       </c>
       <c r="L81" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M81" s="12" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N81" s="13" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O81" s="17" t="n">
         <v>0</v>
@@ -6550,12 +6550,12 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
@@ -6565,12 +6565,12 @@
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
@@ -6601,16 +6601,16 @@
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N82" s="16" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O82" s="17" t="n">
         <v>0</v>
@@ -6622,32 +6622,32 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G83" s="12" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I83" s="12" t="inlineStr">
@@ -6669,52 +6669,52 @@
         <v>5</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N83" s="13" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O83" s="17" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="P83" s="13" t="n">
-        <v>588</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
@@ -6729,49 +6729,49 @@
       </c>
       <c r="H84" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O84" s="17" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J85" s="12" t="n">
@@ -6817,16 +6817,16 @@
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N85" s="13" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O85" s="17" t="n">
         <v>0</v>
@@ -6838,32 +6838,32 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G86" s="15" t="inlineStr">
@@ -6873,49 +6873,49 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K86" s="15" t="n">
-        <v>15.25</v>
+        <v>0</v>
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>700</v>
-      </c>
-      <c r="O86" s="16" t="n">
-        <v>1934.1</v>
+        <v>300</v>
+      </c>
+      <c r="O86" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>126.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H87" s="12" t="inlineStr">
@@ -6957,44 +6957,52 @@
         <v>6</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L87" s="12" t="inlineStr"/>
-      <c r="M87" s="12" t="inlineStr"/>
+        <v>15.25</v>
+      </c>
+      <c r="L87" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="M87" s="12" t="inlineStr">
+        <is>
+          <t>00157816</t>
+        </is>
+      </c>
       <c r="N87" s="13" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="O87" s="13" t="n">
-        <v>0</v>
+        <v>1934.1</v>
       </c>
       <c r="P87" s="13" t="n">
-        <v>0</v>
+        <v>126.83</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
@@ -7004,7 +7012,7 @@
       </c>
       <c r="G88" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H88" s="15" t="inlineStr">
@@ -7014,64 +7022,56 @@
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K88" s="15" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="L88" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-31468</t>
-        </is>
-      </c>
-      <c r="M88" s="15" t="inlineStr">
-        <is>
-          <t>00157346</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L88" s="15" t="inlineStr"/>
+      <c r="M88" s="15" t="inlineStr"/>
       <c r="N88" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O88" s="16" t="n">
-        <v>138.825</v>
+        <v>0</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>15.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G89" s="12" t="inlineStr">
@@ -7081,49 +7081,49 @@
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J89" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="L89" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M89" s="12" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N89" s="13" t="n">
-        <v>210</v>
-      </c>
-      <c r="O89" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O89" s="13" t="n">
+        <v>138.825</v>
       </c>
       <c r="P89" s="13" t="n">
-        <v>0</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
@@ -7133,12 +7133,12 @@
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
@@ -7169,16 +7169,16 @@
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O90" s="17" t="n">
         <v>0</v>
@@ -7190,12 +7190,12 @@
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J91" s="12" t="n">
@@ -7241,16 +7241,16 @@
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N91" s="13" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O91" s="17" t="n">
         <v>0</v>
@@ -7262,12 +7262,12 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
@@ -7302,29 +7302,29 @@
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K92" s="15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="16" t="n">
+        <v>255</v>
+      </c>
+      <c r="O92" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="16" t="n">
@@ -7334,12 +7334,12 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -7349,12 +7349,12 @@
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
@@ -7374,29 +7374,29 @@
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J93" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N93" s="13" t="n">
-        <v>140</v>
-      </c>
-      <c r="O93" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="13" t="n">
@@ -7406,27 +7406,27 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30311</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAEN</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>GeODP - Modification des marges via activation Editique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
@@ -7457,19 +7457,19 @@
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30316</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00154362</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" s="16" t="n">
-        <v>200</v>
+        <v>140</v>
+      </c>
+      <c r="O94" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P94" s="16" t="n">
         <v>0</v>
@@ -7478,32 +7478,32 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30311</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE CAEN</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G95" s="12" t="inlineStr">
@@ -7513,64 +7513,64 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="J95" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30316</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154362</t>
         </is>
       </c>
       <c r="N95" s="13" t="n">
-        <v>690</v>
-      </c>
-      <c r="O95" s="17" t="n">
-        <v>230</v>
+        <v>0</v>
+      </c>
+      <c r="O95" s="13" t="n">
+        <v>200</v>
       </c>
       <c r="P95" s="13" t="n">
-        <v>26.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30044</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>CD29</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>Commande du flux WFS COM pour Inforoute</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="G96" s="15" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H96" s="15" t="inlineStr">
@@ -7590,44 +7590,44 @@
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>1</v>
+        <v>8.75</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30046</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00153621</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="16" t="n">
-        <v>0</v>
+        <v>690</v>
+      </c>
+      <c r="O96" s="17" t="n">
+        <v>230</v>
       </c>
       <c r="P96" s="16" t="n">
-        <v>0</v>
+        <v>26.29</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-30044</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>CD29</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H97" s="12" t="inlineStr">
@@ -7662,23 +7662,23 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J97" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30046</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00153621</t>
         </is>
       </c>
       <c r="N97" s="13" t="n">
@@ -7694,12 +7694,12 @@
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
@@ -7734,33 +7734,33 @@
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>2.42</v>
+        <v>0.25</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O98" s="16" t="n">
-        <v>224.05</v>
+        <v>0</v>
       </c>
       <c r="P98" s="16" t="n">
-        <v>92.70999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -7817,22 +7817,22 @@
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O99" s="17" t="n">
-        <v>62.5</v>
+        <v>0</v>
+      </c>
+      <c r="O99" s="13" t="n">
+        <v>224.05</v>
       </c>
       <c r="P99" s="13" t="n">
-        <v>25.86</v>
+        <v>92.70999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -7889,47 +7889,49 @@
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O100" s="17" t="n">
-        <v>262.5</v>
+        <v>62.5</v>
       </c>
       <c r="P100" s="16" t="n">
-        <v>108.62</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
@@ -7948,64 +7950,62 @@
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J101" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>0.5</v>
+        <v>2.42</v>
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="13" t="n">
-        <v>0</v>
+        <v>787.5</v>
+      </c>
+      <c r="O101" s="17" t="n">
+        <v>262.5</v>
       </c>
       <c r="P101" s="13" t="n">
-        <v>0</v>
+        <v>108.62</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
-        </is>
-      </c>
-      <c r="E102" s="15" t="inlineStr">
-        <is>
-          <t>Migration V2</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v/>
       </c>
       <c r="F102" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G102" s="15" t="inlineStr">
@@ -8015,34 +8015,34 @@
       </c>
       <c r="H102" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>725</v>
-      </c>
-      <c r="O102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="16" t="n">
@@ -8052,30 +8052,32 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
@@ -8085,49 +8087,49 @@
       </c>
       <c r="H103" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J103" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="13" t="n">
-        <v>1351.26</v>
+        <v>725</v>
+      </c>
+      <c r="O103" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P103" s="13" t="n">
-        <v>450.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
@@ -8137,13 +8139,11 @@
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E104" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v/>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
@@ -8162,33 +8162,33 @@
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O104" s="16" t="n">
-        <v>0</v>
+        <v>1351.26</v>
       </c>
       <c r="P104" s="16" t="n">
-        <v>0</v>
+        <v>450.42</v>
       </c>
     </row>
     <row r="105">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
@@ -8461,18 +8461,18 @@
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O108" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="16" t="n">
@@ -8482,12 +8482,12 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
@@ -8497,11 +8497,13 @@
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E109" s="12" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
@@ -8515,34 +8517,34 @@
       </c>
       <c r="H109" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J109" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>4.25</v>
+        <v>1.95</v>
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" s="13" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O109" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="13" t="n">
@@ -8552,12 +8554,12 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
@@ -8567,7 +8569,7 @@
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E110" s="15" t="n">
@@ -8585,65 +8587,63 @@
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>10</v>
+        <v>4.25</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O110" s="16" t="n">
-        <v>1280</v>
+        <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E111" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="n">
+        <v/>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
@@ -8662,58 +8662,60 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>0.25</v>
+        <v>11.5</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O111" s="13" t="n">
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="P111" s="13" t="n">
-        <v>0</v>
+        <v>111.3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-25354</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Duncan HAMELIN</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE PLAN D'ORGON</t>
-        </is>
-      </c>
-      <c r="E112" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
@@ -8732,23 +8734,23 @@
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>28/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26768</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>00141775</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
@@ -8764,22 +8766,22 @@
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-25354</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Duncan HAMELIN</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>MAIRIE DE PLAN D'ORGON</t>
         </is>
       </c>
       <c r="E113" s="12" t="n">
@@ -8802,29 +8804,29 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>28/10/2025</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26768</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00141775</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O113" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="13" t="n">
@@ -8834,28 +8836,26 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E114" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v/>
       </c>
       <c r="F114" s="15" t="inlineStr">
         <is>
@@ -8874,29 +8874,29 @@
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O114" s="16" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O114" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="16" t="n">
@@ -8906,27 +8906,27 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>Script purge de données</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
@@ -8936,27 +8936,35 @@
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H115" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J115" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L115" s="12" t="inlineStr"/>
-      <c r="M115" s="12" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L115" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27578</t>
+        </is>
+      </c>
+      <c r="M115" s="12" t="inlineStr">
+        <is>
+          <t>499043</t>
+        </is>
+      </c>
       <c r="N115" s="13" t="n">
         <v>0</v>
       </c>
@@ -8970,26 +8978,28 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E116" s="15" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E116" s="15" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
@@ -8998,35 +9008,27 @@
       </c>
       <c r="G116" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H116" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L116" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27996</t>
-        </is>
-      </c>
-      <c r="M116" s="15" t="inlineStr">
-        <is>
-          <t>501219</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L116" s="15" t="inlineStr"/>
+      <c r="M116" s="15" t="inlineStr"/>
       <c r="N116" s="16" t="n">
         <v>0</v>
       </c>
@@ -9089,12 +9091,12 @@
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N117" s="13" t="n">
@@ -9110,22 +9112,22 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E118" s="15" t="n">
@@ -9148,23 +9150,23 @@
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
@@ -9180,12 +9182,12 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
@@ -9195,7 +9197,7 @@
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E119" s="12" t="n">
@@ -9218,23 +9220,23 @@
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J119" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>0.75</v>
+        <v>3.25</v>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
@@ -9250,12 +9252,12 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
@@ -9265,7 +9267,7 @@
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
@@ -9288,23 +9290,23 @@
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
         <v>13</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>1.31</v>
+        <v>0.75</v>
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
@@ -9320,22 +9322,22 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
@@ -9353,28 +9355,28 @@
       </c>
       <c r="H121" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
         <v>13</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>1.31</v>
+        <v>0.25</v>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N121" s="13" t="n">
@@ -9405,7 +9407,7 @@
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E122" s="15" t="n">
@@ -9439,12 +9441,12 @@
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
@@ -9509,12 +9511,12 @@
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
@@ -9530,22 +9532,22 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9563,34 +9565,34 @@
       </c>
       <c r="H124" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>0.5</v>
+        <v>1.31</v>
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
-        <v>401</v>
-      </c>
-      <c r="O124" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="16" t="n">
@@ -9600,12 +9602,12 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
@@ -9615,7 +9617,7 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
@@ -9631,20 +9633,32 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H125" s="12" t="inlineStr"/>
+      <c r="H125" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J125" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L125" s="12" t="inlineStr"/>
-      <c r="M125" s="12" t="inlineStr"/>
+        <v>1.31</v>
+      </c>
+      <c r="L125" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27365</t>
+        </is>
+      </c>
+      <c r="M125" s="12" t="inlineStr">
+        <is>
+          <t>491593</t>
+        </is>
+      </c>
       <c r="N125" s="13" t="n">
         <v>0</v>
       </c>
@@ -9658,12 +9672,12 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
@@ -9673,7 +9687,7 @@
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9691,34 +9705,34 @@
       </c>
       <c r="H126" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>8.25</v>
+        <v>0.5</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N126" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" s="16" t="n">
+        <v>401</v>
+      </c>
+      <c r="O126" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="16" t="n">
@@ -9728,12 +9742,12 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
@@ -9743,7 +9757,7 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
@@ -9759,14 +9773,10 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H127" s="12" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H127" s="12" t="inlineStr"/>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
@@ -9775,16 +9785,8 @@
       <c r="K127" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="L127" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28035</t>
-        </is>
-      </c>
-      <c r="M127" s="12" t="inlineStr">
-        <is>
-          <t>468660</t>
-        </is>
-      </c>
+      <c r="L127" s="12" t="inlineStr"/>
+      <c r="M127" s="12" t="inlineStr"/>
       <c r="N127" s="13" t="n">
         <v>0</v>
       </c>
@@ -9798,12 +9800,12 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
@@ -9813,7 +9815,7 @@
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E128" s="15" t="n">
@@ -9831,34 +9833,34 @@
       </c>
       <c r="H128" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="L128" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M128" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N128" s="16" t="n">
-        <v>230</v>
-      </c>
-      <c r="O128" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="16" t="n">
@@ -9868,12 +9870,12 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
@@ -9883,7 +9885,7 @@
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
@@ -9896,23 +9898,35 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H129" s="12" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J129" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L129" s="12" t="inlineStr"/>
-      <c r="M129" s="12" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L129" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28035</t>
+        </is>
+      </c>
+      <c r="M129" s="12" t="inlineStr">
+        <is>
+          <t>468660</t>
+        </is>
+      </c>
       <c r="N129" s="13" t="n">
         <v>0</v>
       </c>
@@ -9926,12 +9940,12 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
@@ -9941,7 +9955,7 @@
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E130" s="15" t="n">
@@ -9959,34 +9973,34 @@
       </c>
       <c r="H130" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O130" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O130" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P130" s="16" t="n">
@@ -9996,22 +10010,22 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
@@ -10024,35 +10038,23 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H131" s="12" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="inlineStr"/>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
         <v>17</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L131" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27568</t>
-        </is>
-      </c>
-      <c r="M131" s="12" t="inlineStr">
-        <is>
-          <t>471958</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L131" s="12" t="inlineStr"/>
+      <c r="M131" s="12" t="inlineStr"/>
       <c r="N131" s="13" t="n">
         <v>0</v>
       </c>
@@ -10066,22 +10068,22 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E132" s="15" t="n">
@@ -10104,23 +10106,23 @@
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L132" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M132" s="15" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N132" s="16" t="n">
@@ -10136,22 +10138,22 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10169,28 +10171,28 @@
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28214</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>458286</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N133" s="13" t="n">
@@ -10206,22 +10208,22 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E134" s="15" t="n">
@@ -10234,7 +10236,7 @@
       </c>
       <c r="G134" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H134" s="15" t="inlineStr">
@@ -10244,17 +10246,25 @@
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="L134" s="15" t="inlineStr"/>
-      <c r="M134" s="15" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L134" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28215</t>
+        </is>
+      </c>
+      <c r="M134" s="15" t="inlineStr">
+        <is>
+          <t>458306</t>
+        </is>
+      </c>
       <c r="N134" s="16" t="n">
         <v>0</v>
       </c>
@@ -10268,22 +10278,22 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
@@ -10296,7 +10306,7 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H135" s="12" t="inlineStr">
@@ -10306,17 +10316,25 @@
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J135" s="12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L135" s="12" t="inlineStr"/>
-      <c r="M135" s="12" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L135" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28214</t>
+        </is>
+      </c>
+      <c r="M135" s="12" t="inlineStr">
+        <is>
+          <t>458286</t>
+        </is>
+      </c>
       <c r="N135" s="13" t="n">
         <v>0</v>
       </c>
@@ -10330,22 +10348,22 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E136" s="15" t="n">
@@ -10353,44 +10371,36 @@
       </c>
       <c r="F136" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G136" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H136" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
         <v>20</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M136" s="15" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L136" s="15" t="inlineStr"/>
+      <c r="M136" s="15" t="inlineStr"/>
       <c r="N136" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O136" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P136" s="16" t="n">
@@ -10400,12 +10410,12 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
@@ -10415,7 +10425,7 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10428,35 +10438,27 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
         <v>20</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="L137" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34362</t>
-        </is>
-      </c>
-      <c r="M137" s="12" t="inlineStr">
-        <is>
-          <t>458057</t>
-        </is>
-      </c>
+        <v>11.25</v>
+      </c>
+      <c r="L137" s="12" t="inlineStr"/>
+      <c r="M137" s="12" t="inlineStr"/>
       <c r="N137" s="13" t="n">
         <v>0</v>
       </c>
@@ -10470,12 +10472,12 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
@@ -10485,7 +10487,7 @@
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10498,35 +10500,27 @@
       </c>
       <c r="G138" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H138" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
         <v>20</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="L138" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28020</t>
-        </is>
-      </c>
-      <c r="M138" s="15" t="inlineStr">
-        <is>
-          <t>458057</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L138" s="15" t="inlineStr"/>
+      <c r="M138" s="15" t="inlineStr"/>
       <c r="N138" s="16" t="n">
         <v>0</v>
       </c>
@@ -10540,22 +10534,22 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10563,7 +10557,7 @@
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
@@ -10573,12 +10567,12 @@
       </c>
       <c r="H139" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
@@ -10589,16 +10583,16 @@
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N139" s="13" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O139" s="17" t="n">
         <v>0</v>
@@ -10610,22 +10604,22 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10638,7 +10632,7 @@
       </c>
       <c r="G140" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H140" s="15" t="inlineStr">
@@ -10648,17 +10642,25 @@
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J140" s="15" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L140" s="15" t="inlineStr"/>
-      <c r="M140" s="15" t="inlineStr"/>
+        <v>0.38</v>
+      </c>
+      <c r="L140" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34362</t>
+        </is>
+      </c>
+      <c r="M140" s="15" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N140" s="16" t="n">
         <v>0</v>
       </c>
@@ -10672,22 +10674,22 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15041</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>CD38</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10700,7 +10702,7 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H141" s="12" t="inlineStr">
@@ -10710,17 +10712,25 @@
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>26/04/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L141" s="12" t="inlineStr"/>
-      <c r="M141" s="12" t="inlineStr"/>
+        <v>0.38</v>
+      </c>
+      <c r="L141" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M141" s="12" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N141" s="13" t="n">
         <v>0</v>
       </c>
@@ -10734,12 +10744,12 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
@@ -10749,7 +10759,7 @@
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10762,7 +10772,7 @@
       </c>
       <c r="G142" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H142" s="15" t="inlineStr">
@@ -10772,29 +10782,29 @@
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28003</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
         <is>
-          <t>412981</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N142" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O142" s="16" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O142" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P142" s="16" t="n">
@@ -10804,12 +10814,12 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
@@ -10819,7 +10829,7 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10842,14 +10852,14 @@
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L143" s="12" t="inlineStr"/>
       <c r="M143" s="12" t="inlineStr"/>
@@ -10866,22 +10876,22 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -10904,14 +10914,14 @@
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L144" s="15" t="inlineStr"/>
       <c r="M144" s="15" t="inlineStr"/>
@@ -10928,12 +10938,12 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
@@ -10943,7 +10953,7 @@
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -10961,22 +10971,30 @@
       </c>
       <c r="H145" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L145" s="12" t="inlineStr"/>
-      <c r="M145" s="12" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L145" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M145" s="12" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N145" s="13" t="n">
         <v>0</v>
       </c>
@@ -10990,22 +11008,22 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11018,7 +11036,7 @@
       </c>
       <c r="G146" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H146" s="15" t="inlineStr">
@@ -11028,25 +11046,17 @@
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L146" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M146" s="15" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L146" s="15" t="inlineStr"/>
+      <c r="M146" s="15" t="inlineStr"/>
       <c r="N146" s="16" t="n">
         <v>0</v>
       </c>
@@ -11060,22 +11070,22 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
@@ -11091,17 +11101,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H147" s="12" t="inlineStr"/>
+      <c r="H147" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L147" s="12" t="inlineStr"/>
       <c r="M147" s="12" t="inlineStr"/>
@@ -11118,22 +11132,22 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E148" s="15" t="n">
@@ -11156,25 +11170,17 @@
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L148" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M148" s="15" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L148" s="15" t="inlineStr"/>
+      <c r="M148" s="15" t="inlineStr"/>
       <c r="N148" s="16" t="n">
         <v>0</v>
       </c>
@@ -11188,12 +11194,12 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[VALENCIENNES] Littéralis Prime</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
@@ -11203,7 +11209,7 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
@@ -11226,14 +11232,14 @@
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L149" s="12" t="inlineStr"/>
       <c r="M149" s="12" t="inlineStr"/>
@@ -11250,12 +11256,12 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
@@ -11265,13 +11271,11 @@
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E150" s="15" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E150" s="15" t="n">
+        <v/>
       </c>
       <c r="F150" s="15" t="inlineStr">
         <is>
@@ -11280,7 +11284,7 @@
       </c>
       <c r="G150" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H150" s="15" t="inlineStr">
@@ -11290,17 +11294,25 @@
       </c>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J150" s="15" t="n">
         <v>35</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L150" s="15" t="inlineStr"/>
-      <c r="M150" s="15" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L150" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M150" s="15" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N150" s="16" t="n">
         <v>0</v>
       </c>
@@ -11314,24 +11326,26 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C151" s="12" t="inlineStr"/>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E151" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E151" s="12" t="n">
+        <v/>
       </c>
       <c r="F151" s="12" t="inlineStr">
         <is>
@@ -11343,21 +11357,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H151" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H151" s="12" t="inlineStr"/>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J151" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L151" s="12" t="inlineStr"/>
       <c r="M151" s="12" t="inlineStr"/>
@@ -11374,12 +11384,12 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr">
@@ -11389,13 +11399,11 @@
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
-        </is>
-      </c>
-      <c r="E152" s="15" t="inlineStr">
-        <is>
-          <t>Montée de version + Pastell</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E152" s="15" t="n">
+        <v/>
       </c>
       <c r="F152" s="15" t="inlineStr">
         <is>
@@ -11409,22 +11417,30 @@
       </c>
       <c r="H152" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L152" s="15" t="inlineStr"/>
-      <c r="M152" s="15" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L152" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M152" s="15" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N152" s="16" t="n">
         <v>0</v>
       </c>
@@ -11438,21 +11454,27 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="C153" s="12" t="inlineStr"/>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E153" s="12" t="inlineStr"/>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E153" s="12" t="n">
+        <v/>
+      </c>
       <c r="F153" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11460,17 +11482,21 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H153" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H153" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="K153" s="12" t="n">
         <v>0.5</v>
@@ -11490,21 +11516,29 @@
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
-        </is>
-      </c>
-      <c r="C154" s="15" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C154" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
-        </is>
-      </c>
-      <c r="E154" s="15" t="inlineStr"/>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E154" s="15" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
       <c r="F154" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11512,20 +11546,24 @@
       </c>
       <c r="G154" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H154" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H154" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I154" s="15" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J154" s="15" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L154" s="15" t="inlineStr"/>
       <c r="M154" s="15" t="inlineStr"/>
@@ -11542,21 +11580,25 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr"/>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
-        </is>
-      </c>
-      <c r="E155" s="12" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11564,36 +11606,32 @@
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H155" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H155" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J155" s="12" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M155" s="12" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="L155" s="12" t="inlineStr"/>
+      <c r="M155" s="12" t="inlineStr"/>
       <c r="N155" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O155" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P155" s="13" t="n">
         <v>0</v>
@@ -11602,21 +11640,29 @@
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C156" s="15" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C156" s="15" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E156" s="15" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E156" s="15" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F156" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11624,56 +11670,52 @@
       </c>
       <c r="G156" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H156" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H156" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J156" s="15" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L156" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M156" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L156" s="15" t="inlineStr"/>
+      <c r="M156" s="15" t="inlineStr"/>
       <c r="N156" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O156" s="16" t="n">
-        <v>595.7</v>
+        <v>0</v>
       </c>
       <c r="P156" s="16" t="n">
-        <v>595.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr"/>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr"/>
@@ -11690,14 +11732,14 @@
       <c r="H157" s="12" t="inlineStr"/>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J157" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L157" s="12" t="inlineStr"/>
       <c r="M157" s="12" t="inlineStr"/>
@@ -11714,18 +11756,18 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PSC-583</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr"/>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E158" s="15" t="inlineStr"/>
@@ -11742,11 +11784,11 @@
       <c r="H158" s="15" t="inlineStr"/>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K158" s="15" t="n">
         <v>0.25</v>
@@ -11764,31 +11806,255 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="18" t="inlineStr">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t>PSC-1315</t>
+        </is>
+      </c>
+      <c r="B159" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE RANG DU FLIERS</t>
+        </is>
+      </c>
+      <c r="C159" s="12" t="inlineStr"/>
+      <c r="D159" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE RANG DU FLIERS</t>
+        </is>
+      </c>
+      <c r="E159" s="12" t="inlineStr"/>
+      <c r="F159" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G159" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H159" s="12" t="inlineStr"/>
+      <c r="I159" s="12" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="J159" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K159" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34778</t>
+        </is>
+      </c>
+      <c r="M159" s="12" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
+      <c r="N159" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="P159" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B160" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C160" s="15" t="inlineStr"/>
+      <c r="D160" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E160" s="15" t="inlineStr"/>
+      <c r="F160" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G160" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H160" s="15" t="inlineStr"/>
+      <c r="I160" s="15" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J160" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K160" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L160" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M160" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N160" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" s="16" t="n">
+        <v>595.7</v>
+      </c>
+      <c r="P160" s="16" t="n">
+        <v>595.7</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="11" t="inlineStr">
+        <is>
+          <t>PSC-850</t>
+        </is>
+      </c>
+      <c r="B161" s="12" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="C161" s="12" t="inlineStr"/>
+      <c r="D161" s="12" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="E161" s="12" t="inlineStr"/>
+      <c r="F161" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G161" s="12" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H161" s="12" t="inlineStr"/>
+      <c r="I161" s="12" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="J161" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K161" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L161" s="12" t="inlineStr"/>
+      <c r="M161" s="12" t="inlineStr"/>
+      <c r="N161" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="14" t="inlineStr">
+        <is>
+          <t>PSC-583</t>
+        </is>
+      </c>
+      <c r="B162" s="15" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="C162" s="15" t="inlineStr"/>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="E162" s="15" t="inlineStr"/>
+      <c r="F162" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G162" s="15" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H162" s="15" t="inlineStr"/>
+      <c r="I162" s="15" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J162" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="K162" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L162" s="15" t="inlineStr"/>
+      <c r="M162" s="15" t="inlineStr"/>
+      <c r="N162" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B159" s="18" t="inlineStr"/>
-      <c r="C159" s="18" t="inlineStr"/>
-      <c r="D159" s="18" t="inlineStr"/>
-      <c r="E159" s="18" t="inlineStr"/>
-      <c r="F159" s="18" t="inlineStr"/>
-      <c r="G159" s="18" t="inlineStr"/>
-      <c r="H159" s="18" t="inlineStr"/>
-      <c r="I159" s="18" t="inlineStr"/>
-      <c r="J159" s="18" t="inlineStr"/>
-      <c r="K159" s="18" t="inlineStr"/>
-      <c r="L159" s="18" t="inlineStr"/>
-      <c r="M159" s="18" t="inlineStr"/>
-      <c r="N159" s="19" t="n">
+      <c r="B163" s="18" t="inlineStr"/>
+      <c r="C163" s="18" t="inlineStr"/>
+      <c r="D163" s="18" t="inlineStr"/>
+      <c r="E163" s="18" t="inlineStr"/>
+      <c r="F163" s="18" t="inlineStr"/>
+      <c r="G163" s="18" t="inlineStr"/>
+      <c r="H163" s="18" t="inlineStr"/>
+      <c r="I163" s="18" t="inlineStr"/>
+      <c r="J163" s="18" t="inlineStr"/>
+      <c r="K163" s="18" t="inlineStr"/>
+      <c r="L163" s="18" t="inlineStr"/>
+      <c r="M163" s="18" t="inlineStr"/>
+      <c r="N163" s="19" t="n">
         <v>46991.995</v>
       </c>
-      <c r="O159" s="19" t="n">
+      <c r="O163" s="19" t="n">
         <v>38207.692</v>
       </c>
-      <c r="P159" s="19" t="n">
-        <v>143.91</v>
+      <c r="P163" s="19" t="n">
+        <v>139.7</v>
       </c>
     </row>
   </sheetData>
@@ -11948,6 +12214,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A159" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId158"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12651,26 +12921,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>187.75</v>
+        <v>192.25</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>38.5</v>
+        <v>41.75</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>16.75</v>
+        <v>17</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>84.5</v>
+        <v>86.5</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>532.88</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
@@ -12712,7 +12982,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>214.5</v>
+        <v>218.25</v>
       </c>
     </row>
   </sheetData>
